--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\cap776\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41EA7C3-8B9C-4F87-B3D2-6DA4CCB0B97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\cap776\CAP-776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41EA7C3-8B9C-4F87-B3D2-6DA4CCB0B97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96C6DBC-7643-4EAA-B10B-D70C2C46960A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1489,8 +1489,12 @@
       <c r="A18" s="13">
         <v>46263</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
+      <c r="B18" s="14">
+        <v>360</v>
+      </c>
+      <c r="C18" s="14">
+        <v>20</v>
+      </c>
       <c r="D18" s="14">
         <v>300</v>
       </c>
@@ -1508,11 +1512,11 @@
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>580</v>
+        <v>960</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>860</v>
+        <v>480</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>63</v>
@@ -1529,8 +1533,12 @@
       <c r="A19" s="13">
         <v>46264</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+      <c r="B19" s="14">
+        <v>360</v>
+      </c>
+      <c r="C19" s="14">
+        <v>20</v>
+      </c>
       <c r="D19" s="14">
         <v>260</v>
       </c>
@@ -1548,11 +1556,11 @@
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>580</v>
+        <v>960</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>860</v>
+        <v>480</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>68</v>
@@ -1571,8 +1579,12 @@
       <c r="A20" s="13">
         <v>46265</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
+      <c r="B20" s="14">
+        <v>360</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
       <c r="D20" s="14">
         <v>300</v>
       </c>
@@ -1590,11 +1602,11 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>660</v>
+        <v>1020</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>780</v>
+        <v>420</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>68</v>
@@ -1613,8 +1625,12 @@
       <c r="A21" s="13">
         <v>46266</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+      <c r="B21" s="14">
+        <v>300</v>
+      </c>
+      <c r="C21" s="14">
+        <v>20</v>
+      </c>
       <c r="D21" s="14">
         <v>350</v>
       </c>
@@ -1632,11 +1648,11 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1095</v>
+        <v>1415</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>345</v>
+        <v>25</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>68</v>
@@ -1655,8 +1671,12 @@
       <c r="A22" s="13">
         <v>46267</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>20</v>
+      </c>
       <c r="D22" s="14">
         <v>200</v>
       </c>
@@ -1674,11 +1694,11 @@
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>1310</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>130</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>73</v>
@@ -1697,8 +1717,12 @@
       <c r="A23" s="13">
         <v>46268</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
+      <c r="B23" s="14">
+        <v>300</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
       <c r="D23" s="14">
         <v>200</v>
       </c>
@@ -1716,11 +1740,11 @@
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>625</v>
+        <v>925</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>815</v>
+        <v>515</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>73</v>
@@ -1739,8 +1763,12 @@
       <c r="A24" s="13">
         <v>46269</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
+      <c r="B24" s="14">
+        <v>360</v>
+      </c>
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
       <c r="D24" s="14">
         <v>180</v>
       </c>
@@ -1758,11 +1786,11 @@
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>670</v>
+        <v>1050</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>770</v>
+        <v>390</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>49</v>
@@ -1781,8 +1809,12 @@
       <c r="A25" s="13">
         <v>46270</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
       <c r="D25" s="14">
         <v>300</v>
       </c>
@@ -1800,11 +1832,11 @@
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>700</v>
+        <v>1120</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>740</v>
+        <v>320</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>68</v>
@@ -1821,8 +1853,12 @@
       <c r="A26" s="13">
         <v>46271</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
       <c r="D26" s="14">
         <v>300</v>
       </c>
@@ -1840,11 +1876,11 @@
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>700</v>
+        <v>1120</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>740</v>
+        <v>320</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>66</v>
@@ -1861,8 +1897,12 @@
       <c r="A27" s="13">
         <v>46272</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>20</v>
+      </c>
       <c r="D27" s="14">
         <v>200</v>
       </c>
@@ -1880,11 +1920,11 @@
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>660</v>
+        <v>1100</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>780</v>
+        <v>340</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>77</v>
@@ -1903,8 +1943,12 @@
       <c r="A28" s="13">
         <v>46273</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
       <c r="D28" s="14">
         <v>180</v>
       </c>
@@ -1922,11 +1966,11 @@
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>710</v>
+        <v>1130</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>730</v>
+        <v>310</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>78</v>
@@ -1942,179 +1986,355 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>150</v>
+      </c>
+      <c r="E29" s="14">
+        <v>68</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>100</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>938</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>502</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>140</v>
+      </c>
+      <c r="E30" s="14">
+        <v>75</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>120</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>435</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>172</v>
+      </c>
+      <c r="E31" s="14">
+        <v>90</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>123</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>805</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>635</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>135</v>
+      </c>
+      <c r="E32" s="14">
+        <v>49</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>40</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>644</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>796</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>103</v>
+      </c>
+      <c r="E33" s="14">
+        <v>56</v>
+      </c>
+      <c r="F33" s="14">
+        <v>200</v>
+      </c>
+      <c r="G33" s="14">
+        <v>4</v>
+      </c>
+      <c r="H33" s="14">
+        <v>60</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>839</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>601</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>106</v>
+      </c>
+      <c r="E34" s="14">
+        <v>67</v>
+      </c>
+      <c r="F34" s="14">
+        <v>350</v>
+      </c>
+      <c r="G34" s="14">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14">
+        <v>68</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1011</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>429</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B35" s="14">
+        <v>360</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>182</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>75</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>997</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>443</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <v>145</v>
+      </c>
+      <c r="E36" s="14">
+        <v>75</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>70</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>530</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96C6DBC-7643-4EAA-B10B-D70C2C46960A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0E0208-D1C8-4604-BA1F-DFDA3E336584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>fantastic ca of dbms</t>
+  </si>
+  <si>
+    <t>frushted due to C.A  of analytical skill</t>
   </si>
 </sst>
 </file>
@@ -2338,69 +2341,137 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B37" s="14">
+        <v>480</v>
+      </c>
+      <c r="C37" s="14">
+        <v>10</v>
+      </c>
+      <c r="D37" s="14">
+        <v>300</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>60</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="14">
+        <v>360</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>300</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>60</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="14">
+        <v>480</v>
+      </c>
+      <c r="C39" s="14">
+        <v>10</v>
+      </c>
+      <c r="D39" s="14">
+        <v>180</v>
+      </c>
+      <c r="E39" s="14">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>60</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+        <v>710</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0E0208-D1C8-4604-BA1F-DFDA3E336584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3F6AD6-7EFF-46CE-9A4D-489055E648E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2475,47 +2475,91 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="14">
+        <v>420</v>
+      </c>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <v>240</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>120</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="14">
+        <v>420</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <v>240</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>200</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
+      </c>
+      <c r="H41" s="14">
+        <v>120</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3F6AD6-7EFF-46CE-9A4D-489055E648E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8086D8-DDBB-4F29-9E33-C03C8BA70A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,25 +208,7 @@
     <t>AUGUST</t>
   </si>
   <si>
-    <t>NICE</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>GOOD</t>
-  </si>
-  <si>
-    <t>NOT BAD</t>
-  </si>
-  <si>
     <t>medium</t>
-  </si>
-  <si>
-    <t>exciting</t>
   </si>
   <si>
     <t>high</t>
@@ -235,13 +217,7 @@
     <t>very excited and exploring new things about cooding .</t>
   </si>
   <si>
-    <t>very nice</t>
-  </si>
-  <si>
     <t>I was missing my brother on account of rakhi</t>
-  </si>
-  <si>
-    <t>nice</t>
   </si>
   <si>
     <t>low</t>
@@ -256,9 +232,6 @@
     <t>nice weathjer = good mood</t>
   </si>
   <si>
-    <t>good</t>
-  </si>
-  <si>
     <t>due to fever am not done well in my english  C.A .</t>
   </si>
   <si>
@@ -268,19 +241,25 @@
     <t>not bad</t>
   </si>
   <si>
-    <t>satifying day</t>
-  </si>
-  <si>
-    <t>excellent</t>
-  </si>
-  <si>
-    <t>very high</t>
-  </si>
-  <si>
     <t>fantastic ca of dbms</t>
   </si>
   <si>
     <t>frushted due to C.A  of analytical skill</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -1144,13 +1123,13 @@
         <v>220</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
         <v>58</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>59</v>
       </c>
       <c r="N7" s="17"/>
     </row>
@@ -1188,13 +1167,13 @@
         <v>285</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N8" s="17"/>
     </row>
@@ -1232,13 +1211,13 @@
         <v>150</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N9" s="17"/>
     </row>
@@ -1389,10 +1368,10 @@
         <v>49</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N15" s="17"/>
     </row>
@@ -1430,16 +1409,16 @@
         <v>640</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1476,16 +1455,16 @@
         <v>390</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1522,13 +1501,13 @@
         <v>480</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N18" s="17"/>
     </row>
@@ -1566,16 +1545,16 @@
         <v>480</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1612,16 +1591,16 @@
         <v>420</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1658,16 +1637,16 @@
         <v>25</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="L21" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N21" s="17" t="s">
         <v>64</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1704,16 +1683,16 @@
         <v>130</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1750,16 +1729,16 @@
         <v>515</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1799,13 +1778,13 @@
         <v>49</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1842,13 +1821,13 @@
         <v>320</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N25" s="17"/>
     </row>
@@ -1886,13 +1865,13 @@
         <v>320</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N26" s="17"/>
     </row>
@@ -1930,16 +1909,16 @@
         <v>340</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -1976,16 +1955,16 @@
         <v>310</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2025,10 +2004,10 @@
         <v>49</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N29" s="17"/>
     </row>
@@ -2066,13 +2045,13 @@
         <v>435</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N30" s="17"/>
     </row>
@@ -2110,13 +2089,13 @@
         <v>635</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N31" s="17"/>
     </row>
@@ -2154,13 +2133,13 @@
         <v>796</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N32" s="17"/>
     </row>
@@ -2198,13 +2177,13 @@
         <v>601</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N33" s="17"/>
     </row>
@@ -2245,10 +2224,10 @@
         <v>49</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N34" s="17"/>
     </row>
@@ -2286,13 +2265,13 @@
         <v>443</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N35" s="17"/>
     </row>
@@ -2330,13 +2309,13 @@
         <v>530</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N36" s="17"/>
     </row>
@@ -2374,16 +2353,16 @@
         <v>340</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -2420,13 +2399,13 @@
         <v>720</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N38" s="17"/>
     </row>
@@ -2464,13 +2443,13 @@
         <v>710</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N39" s="17"/>
     </row>
@@ -2508,13 +2487,13 @@
         <v>660</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N40" s="17"/>
     </row>
@@ -2552,36 +2531,58 @@
         <v>460</v>
       </c>
       <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N41" s="17"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B42" s="14">
+        <v>360</v>
+      </c>
+      <c r="C42" s="14">
+        <v>20</v>
+      </c>
+      <c r="D42" s="14">
+        <v>180</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>60</v>
+      </c>
+      <c r="I42" s="15">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J42" s="15">
+        <f t="shared" si="1"/>
+        <v>470</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M42" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="L41" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M41" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8086D8-DDBB-4F29-9E33-C03C8BA70A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AB8AD2-304A-41E9-AEB1-67DE97CEC3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,19 +208,10 @@
     <t>AUGUST</t>
   </si>
   <si>
-    <t>medium</t>
-  </si>
-  <si>
-    <t>high</t>
-  </si>
-  <si>
     <t>very excited and exploring new things about cooding .</t>
   </si>
   <si>
     <t>I was missing my brother on account of rakhi</t>
-  </si>
-  <si>
-    <t>low</t>
   </si>
   <si>
     <t>due to fever</t>
@@ -260,6 +251,9 @@
   </si>
   <si>
     <t>Excellent</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -910,7 +904,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N400"/>
   <sheetFormatPr defaultColWidth="18.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
@@ -1069,11 +1063,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I68" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J68" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1129,7 +1123,7 @@
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="N7" s="17"/>
     </row>
@@ -1170,10 +1164,10 @@
         <v>49</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N8" s="17"/>
     </row>
@@ -1211,13 +1205,13 @@
         <v>150</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="N9" s="17"/>
     </row>
@@ -1371,7 +1365,7 @@
         <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N15" s="17"/>
     </row>
@@ -1409,16 +1403,16 @@
         <v>640</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L16" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M16" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="M16" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N16" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1458,13 +1452,13 @@
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1501,13 +1495,13 @@
         <v>480</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L18" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N18" s="17"/>
     </row>
@@ -1548,13 +1542,13 @@
         <v>49</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1594,13 +1588,13 @@
         <v>49</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1640,13 +1634,13 @@
         <v>49</v>
       </c>
       <c r="L21" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M21" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="M21" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N21" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1689,10 +1683,10 @@
         <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1735,10 +1729,10 @@
         <v>50</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1778,13 +1772,13 @@
         <v>49</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1821,13 +1815,13 @@
         <v>320</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="N25" s="17"/>
     </row>
@@ -1865,13 +1859,13 @@
         <v>320</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L26" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M26" s="16" t="s">
         <v>72</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="N26" s="17"/>
     </row>
@@ -1912,13 +1906,13 @@
         <v>49</v>
       </c>
       <c r="L27" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M27" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="M27" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N27" s="17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -1955,16 +1949,16 @@
         <v>310</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L28" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M28" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="M28" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="N28" s="17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2007,7 +2001,7 @@
         <v>50</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N29" s="17"/>
     </row>
@@ -2048,10 +2042,10 @@
         <v>49</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="N30" s="17"/>
     </row>
@@ -2089,13 +2083,13 @@
         <v>635</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L31" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M31" s="16" t="s">
         <v>72</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="N31" s="17"/>
     </row>
@@ -2133,13 +2127,13 @@
         <v>796</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L32" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M32" s="16" t="s">
         <v>72</v>
-      </c>
-      <c r="M32" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="N32" s="17"/>
     </row>
@@ -2177,13 +2171,13 @@
         <v>601</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L33" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M33" s="16" t="s">
         <v>72</v>
-      </c>
-      <c r="M33" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="N33" s="17"/>
     </row>
@@ -2224,10 +2218,10 @@
         <v>49</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N34" s="17"/>
     </row>
@@ -2265,13 +2259,13 @@
         <v>443</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="N35" s="17"/>
     </row>
@@ -2309,13 +2303,13 @@
         <v>530</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L36" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M36" s="16" t="s">
         <v>72</v>
-      </c>
-      <c r="M36" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="N36" s="17"/>
     </row>
@@ -2359,10 +2353,10 @@
         <v>50</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -2402,10 +2396,10 @@
         <v>49</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N38" s="17"/>
     </row>
@@ -2446,10 +2440,10 @@
         <v>49</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="N39" s="17"/>
     </row>
@@ -2487,13 +2481,13 @@
         <v>660</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L40" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M40" s="16" t="s">
         <v>72</v>
-      </c>
-      <c r="M40" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="N40" s="17"/>
     </row>
@@ -2537,7 +2531,7 @@
         <v>50</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N41" s="17"/>
     </row>
@@ -2546,7 +2540,7 @@
         <v>46287</v>
       </c>
       <c r="B42" s="14">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="C42" s="14">
         <v>20</v>
@@ -2555,7 +2549,7 @@
         <v>180</v>
       </c>
       <c r="E42" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F42" s="14">
         <v>350</v>
@@ -2568,65 +2562,109 @@
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>970</v>
+        <v>1150</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
+        <v>290</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="14">
+        <v>480</v>
+      </c>
+      <c r="C43" s="14">
+        <v>40</v>
+      </c>
+      <c r="D43" s="14">
+        <v>240</v>
+      </c>
+      <c r="E43" s="14">
+        <v>120</v>
+      </c>
+      <c r="F43" s="14">
+        <v>350</v>
+      </c>
+      <c r="G43" s="14">
+        <v>7</v>
+      </c>
+      <c r="H43" s="14">
+        <v>60</v>
+      </c>
+      <c r="I43" s="15">
+        <f t="shared" si="0"/>
+        <v>1290</v>
+      </c>
+      <c r="J43" s="15">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="17"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="14">
+        <v>480</v>
+      </c>
+      <c r="C44" s="14">
+        <v>40</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>50</v>
+      </c>
+      <c r="F44" s="14">
+        <v>200</v>
+      </c>
+      <c r="G44" s="14">
+        <v>4</v>
+      </c>
+      <c r="H44" s="14">
+        <v>80</v>
+      </c>
+      <c r="I44" s="15">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J44" s="15">
+        <f t="shared" si="1"/>
         <v>470</v>
       </c>
-      <c r="K42" s="16" t="s">
+      <c r="K44" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L42" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="M42" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
+      <c r="L44" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -3167,11 +3205,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3189,11 +3227,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -4575,11 +4613,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I133:I196" si="4">IF(SUM(B133:F133,H133)=0,"",SUM(B133:F133,H133))</f>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J133:J196" si="5">IF(I133="","",1440-I133)</f>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4597,11 +4635,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -5983,11 +6021,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I197:I260" si="6">IF(SUM(B197:F197,H197)=0,"",SUM(B197:F197,H197))</f>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J197:J260" si="7">IF(I197="","",1440-I197)</f>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6005,11 +6043,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -7391,11 +7429,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I261:I324" si="8">IF(SUM(B261:F261,H261)=0,"",SUM(B261:F261,H261))</f>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J261:J324" si="9">IF(I261="","",1440-I261)</f>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7413,11 +7451,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -8799,11 +8837,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I325:I388" si="10">IF(SUM(B325:F325,H325)=0,"",SUM(B325:F325,H325))</f>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J325:J388" si="11">IF(I325="","",1440-I325)</f>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8821,11 +8859,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -10207,11 +10245,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I389:I400" si="12">IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J389:J400" si="13">IF(I389="","",1440-I389)</f>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10229,11 +10267,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10461,28 +10499,6 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A401" s="13"/>
-      <c r="B401" s="14"/>
-      <c r="C401" s="14"/>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-      <c r="F401" s="14"/>
-      <c r="G401" s="14"/>
-      <c r="H401" s="14"/>
-      <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="16"/>
-      <c r="L401" s="16"/>
-      <c r="M401" s="16"/>
-      <c r="N401" s="17"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10492,21 +10508,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J400">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L400" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M400" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AB8AD2-304A-41E9-AEB1-67DE97CEC3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FE9A2A-23C8-41A0-B374-7E162FF628E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2668,47 +2668,91 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B45" s="14">
+        <v>480</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>180</v>
+      </c>
+      <c r="E45" s="14">
+        <v>60</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>60</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
+        <v>380</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B46" s="14">
+        <v>480</v>
+      </c>
+      <c r="C46" s="14">
+        <v>20</v>
+      </c>
+      <c r="D46" s="14">
+        <v>120</v>
+      </c>
+      <c r="E46" s="14">
+        <v>60</v>
+      </c>
+      <c r="F46" s="14">
+        <v>150</v>
+      </c>
+      <c r="G46" s="14">
+        <v>3</v>
+      </c>
+      <c r="H46" s="14">
+        <v>60</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FE9A2A-23C8-41A0-B374-7E162FF628E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823376EC-2956-451C-981B-951DF21AE260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -2756,135 +2762,267 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B47" s="14">
+        <v>480</v>
+      </c>
+      <c r="C47" s="14">
+        <v>10</v>
+      </c>
+      <c r="D47" s="14">
+        <v>0</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>240</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+        <v>710</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B48" s="14">
+        <v>480</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>0</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>200</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
+        <v>760</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B49" s="14">
+        <v>480</v>
+      </c>
+      <c r="C49" s="14">
+        <v>0</v>
+      </c>
+      <c r="D49" s="14">
+        <v>0</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>180</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
+        <v>780</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B50" s="14">
+        <v>480</v>
+      </c>
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <v>0</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>240</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B51" s="14">
+        <v>480</v>
+      </c>
+      <c r="C51" s="14">
+        <v>30</v>
+      </c>
+      <c r="D51" s="14">
+        <v>60</v>
+      </c>
+      <c r="E51" s="14">
+        <v>30</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>180</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B52" s="14">
+        <v>480</v>
+      </c>
+      <c r="C52" s="14">
+        <v>30</v>
+      </c>
+      <c r="D52" s="14">
+        <v>60</v>
+      </c>
+      <c r="E52" s="14">
+        <v>60</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>240</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823376EC-2956-451C-981B-951DF21AE260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B396D4-B70D-4779-8682-79841A63E2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3026,201 +3026,399 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B53" s="14">
+        <v>540</v>
+      </c>
+      <c r="C53" s="14">
+        <v>20</v>
+      </c>
+      <c r="D53" s="14">
+        <v>360</v>
+      </c>
+      <c r="E53" s="14">
+        <v>50</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>120</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
+        <v>350</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B54" s="14">
+        <v>480</v>
+      </c>
+      <c r="C54" s="14">
+        <v>25</v>
+      </c>
+      <c r="D54" s="14">
+        <v>340</v>
+      </c>
+      <c r="E54" s="14">
+        <v>45</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>120</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B55" s="14">
+        <v>480</v>
+      </c>
+      <c r="C55" s="14">
+        <v>35</v>
+      </c>
+      <c r="D55" s="14">
+        <v>350</v>
+      </c>
+      <c r="E55" s="14">
+        <v>60</v>
+      </c>
+      <c r="F55" s="14">
+        <v>200</v>
+      </c>
+      <c r="G55" s="14">
+        <v>4</v>
+      </c>
+      <c r="H55" s="14">
+        <v>120</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1245</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
+        <v>195</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B56" s="14">
+        <v>420</v>
+      </c>
+      <c r="C56" s="14">
+        <v>25</v>
+      </c>
+      <c r="D56" s="14">
+        <v>300</v>
+      </c>
+      <c r="E56" s="14">
+        <v>60</v>
+      </c>
+      <c r="F56" s="14">
+        <v>350</v>
+      </c>
+      <c r="G56" s="14">
+        <v>7</v>
+      </c>
+      <c r="H56" s="14">
+        <v>120</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1275</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
+        <v>165</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B57" s="14">
+        <v>420</v>
+      </c>
+      <c r="C57" s="14">
+        <v>20</v>
+      </c>
+      <c r="D57" s="14">
+        <v>240</v>
+      </c>
+      <c r="E57" s="14">
+        <v>30</v>
+      </c>
+      <c r="F57" s="14">
+        <v>350</v>
+      </c>
+      <c r="G57" s="14">
+        <v>7</v>
+      </c>
+      <c r="H57" s="14">
+        <v>180</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
+        <v>200</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="14">
+        <v>360</v>
+      </c>
+      <c r="C58" s="14">
+        <v>20</v>
+      </c>
+      <c r="D58" s="14">
+        <v>300</v>
+      </c>
+      <c r="E58" s="14">
+        <v>45</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>180</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
+        <v>535</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B59" s="14">
+        <v>420</v>
+      </c>
+      <c r="C59" s="14">
+        <v>10</v>
+      </c>
+      <c r="D59" s="14">
+        <v>360</v>
+      </c>
+      <c r="E59" s="14">
+        <v>45</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>360</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1195</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
+        <v>245</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B60" s="14">
+        <v>420</v>
+      </c>
+      <c r="C60" s="14">
+        <v>10</v>
+      </c>
+      <c r="D60" s="14">
+        <v>180</v>
+      </c>
+      <c r="E60" s="14">
+        <v>40</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>360</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B61" s="14">
+        <v>480</v>
+      </c>
+      <c r="C61" s="14">
+        <v>30</v>
+      </c>
+      <c r="D61" s="14">
+        <v>240</v>
+      </c>
+      <c r="E61" s="14">
+        <v>60</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>240</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B396D4-B70D-4779-8682-79841A63E2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DAEF8A-A6BD-4655-A558-5BFE3A02BA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3422,25 +3422,47 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B62" s="14">
+        <v>420</v>
+      </c>
+      <c r="C62" s="14">
+        <v>20</v>
+      </c>
+      <c r="D62" s="14">
+        <v>240</v>
+      </c>
+      <c r="E62" s="14">
+        <v>0</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>300</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DAEF8A-A6BD-4655-A558-5BFE3A02BA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3094ECC3-3C32-4CD5-8603-02D58A49686B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3466,47 +3466,91 @@
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B63" s="14">
+        <v>420</v>
+      </c>
+      <c r="C63" s="14">
+        <v>30</v>
+      </c>
+      <c r="D63" s="14">
+        <v>240</v>
+      </c>
+      <c r="E63" s="14">
+        <v>120</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>300</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
+        <v>330</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B64" s="14">
+        <v>420</v>
+      </c>
+      <c r="C64" s="14">
+        <v>30</v>
+      </c>
+      <c r="D64" s="14">
+        <v>240</v>
+      </c>
+      <c r="E64" s="14">
+        <v>120</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>180</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3094ECC3-3C32-4CD5-8603-02D58A49686B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A459B4-8897-4698-BBDE-612FBE046410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3554,47 +3554,91 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="14">
+        <v>420</v>
+      </c>
+      <c r="C65" s="14">
+        <v>20</v>
+      </c>
+      <c r="D65" s="14">
+        <v>180</v>
+      </c>
+      <c r="E65" s="14">
+        <v>60</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>180</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
+        <v>580</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="14">
+        <v>420</v>
+      </c>
+      <c r="C66" s="14">
+        <v>30</v>
+      </c>
+      <c r="D66" s="14">
+        <v>300</v>
+      </c>
+      <c r="E66" s="14">
+        <v>120</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>120</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A459B4-8897-4698-BBDE-612FBE046410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBC7E58-5E03-47CF-B0ED-982E17C479FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3642,69 +3642,135 @@
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="14">
+        <v>360</v>
+      </c>
+      <c r="C67" s="14">
+        <v>20</v>
+      </c>
+      <c r="D67" s="14">
+        <v>120</v>
+      </c>
+      <c r="E67" s="14">
+        <v>60</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>180</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
+        <v>700</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="14">
+        <v>480</v>
+      </c>
+      <c r="C68" s="14">
+        <v>20</v>
+      </c>
+      <c r="D68" s="14">
+        <v>120</v>
+      </c>
+      <c r="E68" s="14">
+        <v>120</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>120</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
+        <v>580</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B69" s="14">
+        <v>360</v>
+      </c>
+      <c r="C69" s="14">
+        <v>20</v>
+      </c>
+      <c r="D69" s="14">
+        <v>60</v>
+      </c>
+      <c r="E69" s="14">
+        <v>20</v>
+      </c>
+      <c r="F69" s="14">
+        <v>3</v>
+      </c>
+      <c r="G69" s="14">
+        <v>3</v>
+      </c>
+      <c r="H69" s="14">
+        <v>120</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>583</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
+        <v>857</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBC7E58-5E03-47CF-B0ED-982E17C479FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118D1CDA-8B2C-4061-846E-144225C5414A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3746,7 +3746,7 @@
         <v>20</v>
       </c>
       <c r="F69" s="14">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="G69" s="14">
         <v>3</v>
@@ -3756,11 +3756,11 @@
       </c>
       <c r="I69" s="15">
         <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
-        <v>583</v>
+        <v>730</v>
       </c>
       <c r="J69" s="15">
         <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
-        <v>857</v>
+        <v>710</v>
       </c>
       <c r="K69" s="16" t="s">
         <v>49</v>
@@ -3774,113 +3774,223 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B70" s="14">
+        <v>240</v>
+      </c>
+      <c r="C70" s="14">
+        <v>20</v>
+      </c>
+      <c r="D70" s="14">
+        <v>120</v>
+      </c>
+      <c r="E70" s="14">
+        <v>120</v>
+      </c>
+      <c r="F70" s="14">
+        <v>150</v>
+      </c>
+      <c r="G70" s="14">
+        <v>3</v>
+      </c>
+      <c r="H70" s="14">
+        <v>120</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
+        <v>670</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B71" s="14">
+        <v>360</v>
+      </c>
+      <c r="C71" s="14">
+        <v>60</v>
+      </c>
+      <c r="D71" s="14">
+        <v>300</v>
+      </c>
+      <c r="E71" s="14">
+        <v>180</v>
+      </c>
+      <c r="F71" s="14">
+        <v>350</v>
+      </c>
+      <c r="G71" s="14">
+        <v>7</v>
+      </c>
+      <c r="H71" s="14">
+        <v>120</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
+        <v>70</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="14">
+        <v>360</v>
+      </c>
+      <c r="C72" s="14">
+        <v>50</v>
+      </c>
+      <c r="D72" s="14">
+        <v>360</v>
+      </c>
+      <c r="E72" s="14">
+        <v>240</v>
+      </c>
+      <c r="F72" s="14">
+        <v>150</v>
+      </c>
+      <c r="G72" s="14">
+        <v>3</v>
+      </c>
+      <c r="H72" s="14">
+        <v>60</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="14">
+        <v>420</v>
+      </c>
+      <c r="C73" s="14">
+        <v>60</v>
+      </c>
+      <c r="D73" s="14">
+        <v>300</v>
+      </c>
+      <c r="E73" s="14">
+        <v>60</v>
+      </c>
+      <c r="F73" s="14">
+        <v>200</v>
+      </c>
+      <c r="G73" s="14">
+        <v>4</v>
+      </c>
+      <c r="H73" s="14">
+        <v>80</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="14">
+        <v>360</v>
+      </c>
+      <c r="C74" s="14">
+        <v>40</v>
+      </c>
+      <c r="D74" s="14">
+        <v>300</v>
+      </c>
+      <c r="E74" s="14">
+        <v>60</v>
+      </c>
+      <c r="F74" s="14">
+        <v>0</v>
+      </c>
+      <c r="G74" s="14">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14">
+        <v>120</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
+        <v>560</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118D1CDA-8B2C-4061-846E-144225C5414A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894D659C-5179-46E1-8E14-325CAEE846C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3994,47 +3994,91 @@
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B75" s="14">
+        <v>360</v>
+      </c>
+      <c r="C75" s="14">
+        <v>60</v>
+      </c>
+      <c r="D75" s="14">
+        <v>180</v>
+      </c>
+      <c r="E75" s="14">
+        <v>60</v>
+      </c>
+      <c r="F75" s="14">
+        <v>0</v>
+      </c>
+      <c r="G75" s="14">
+        <v>0</v>
+      </c>
+      <c r="H75" s="14">
+        <v>150</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B76" s="14">
+        <v>350</v>
+      </c>
+      <c r="C76" s="14">
+        <v>50</v>
+      </c>
+      <c r="D76" s="14">
+        <v>240</v>
+      </c>
+      <c r="E76" s="14">
+        <v>20</v>
+      </c>
+      <c r="F76" s="14">
+        <v>0</v>
+      </c>
+      <c r="G76" s="14">
+        <v>0</v>
+      </c>
+      <c r="H76" s="14">
+        <v>180</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603160.xlsx
+++ b/12603160.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894D659C-5179-46E1-8E14-325CAEE846C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65EFCC8-7D13-4B2C-A0FA-8E589FC921B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4082,91 +4082,179 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="A77" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B77" s="14">
+        <v>420</v>
+      </c>
+      <c r="C77" s="14">
+        <v>60</v>
+      </c>
+      <c r="D77" s="14">
+        <v>240</v>
+      </c>
+      <c r="E77" s="14">
+        <v>60</v>
+      </c>
+      <c r="F77" s="14">
+        <v>200</v>
+      </c>
+      <c r="G77" s="14">
+        <v>4</v>
+      </c>
+      <c r="H77" s="14">
+        <v>120</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
+        <v>340</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+      <c r="A78" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B78" s="14">
+        <v>420</v>
+      </c>
+      <c r="C78" s="14">
+        <v>60</v>
+      </c>
+      <c r="D78" s="14">
+        <v>120</v>
+      </c>
+      <c r="E78" s="14">
+        <v>60</v>
+      </c>
+      <c r="F78" s="14">
+        <v>300</v>
+      </c>
+      <c r="G78" s="14">
+        <v>6</v>
+      </c>
+      <c r="H78" s="14">
+        <v>120</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+      <c r="A79" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B79" s="14">
+        <v>480</v>
+      </c>
+      <c r="C79" s="14">
+        <v>60</v>
+      </c>
+      <c r="D79" s="14">
+        <v>180</v>
+      </c>
+      <c r="E79" s="14">
+        <v>120</v>
+      </c>
+      <c r="F79" s="14">
+        <v>200</v>
+      </c>
+      <c r="G79" s="14">
+        <v>4</v>
+      </c>
+      <c r="H79" s="14">
+        <v>80</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N79" s="17"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="15" t="str">
+      <c r="A80" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B80" s="14">
+        <v>420</v>
+      </c>
+      <c r="C80" s="14">
+        <v>60</v>
+      </c>
+      <c r="D80" s="14">
+        <v>240</v>
+      </c>
+      <c r="E80" s="14">
+        <v>120</v>
+      </c>
+      <c r="F80" s="14">
+        <v>250</v>
+      </c>
+      <c r="G80" s="14">
+        <v>5</v>
+      </c>
+      <c r="H80" s="14">
+        <v>180</v>
+      </c>
+      <c r="I80" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J80" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="K80" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L80" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M80" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N80" s="17"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
